--- a/reports/Belarus_REEV_Car_Import_Duties_2026-09.xlsx
+++ b/reports/Belarus_REEV_Car_Import_Duties_2026-09.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="504">
   <si>
     <r>
       <rPr>
@@ -1006,7 +1006,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；② 消费税：白俄对乘用车不征，俄罗斯按马力征收（</t>
+      <t xml:space="preserve">；② 消费税：白俄《税法典》应税消费品清单中没有乘用车；俄罗斯按马力征收，</t>
     </r>
     <r>
       <rPr>
@@ -1023,7 +1023,41 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年 </t>
+      <t xml:space="preserve">年为：≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
     </r>
     <r>
       <rPr>
@@ -1049,7 +1083,143 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">64 </t>
+      <t xml:space="preserve">64</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">150–200 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">613</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200–300 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1004</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300–400 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1711</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt;500 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1829 </t>
     </r>
     <r>
       <rPr>
@@ -1074,75 +1244,58 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">马力，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">150–200 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">613 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">卢布</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力，更高档位更高）；③ 报废税：白俄个人为固定低额，俄罗斯自 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2025-12-01 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起与功率挂钩，增程式和纯电车的个人优惠只适用于 </t>
+      <t xml:space="preserve">马力；③ 报废税：白俄个人为固定低额；俄罗斯为 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万卢布基础额乘以系数（按功率、车龄），个人优惠（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,400 / 5,200 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">卢布）对燃油车限 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">160 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力以内，对增程式和纯电车只限 </t>
     </r>
     <r>
       <rPr>
@@ -1159,58 +1312,41 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">马力以下，实际上几乎全部按商业税率征收（例：理想 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">L7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">197 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年约 </t>
+      <t xml:space="preserve">马力以内（按电机 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟最大功率），所以增程车实际都按商业系数缴纳（例：理想 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">约 </t>
     </r>
     <r>
       <rPr>
@@ -1227,11 +1363,79 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">万卢布）。同一辆新增程车，在俄罗斯的税费通常是白俄的数倍（见“俄罗斯对比测算”）。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">S33, S34, S35, S36, S37, S39</t>
+      <t xml:space="preserve">万卢布；新车 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt;205.95 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千瓦时系数 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">152</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，约 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">304 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万卢布）。同一辆新增程车，在俄罗斯的税费约为白俄的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍以上（见“俄罗斯对比测算”）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S33, S34, S39, S43, S44, S37, S46, S49</t>
   </si>
   <si>
     <t xml:space="preserve">二、使用说明</t>
@@ -2101,10 +2305,34 @@
     <t xml:space="preserve">无</t>
   </si>
   <si>
-    <t xml:space="preserve">白俄不对乘用车征收消费税（与俄罗斯不同）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S21</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">白俄《税法典》第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">150 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">条应税消费品清单中没有乘用车（与俄罗斯不同）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S39, S40, S22</t>
   </si>
   <si>
     <t xml:space="preserve">报废税</t>
@@ -2652,6 +2880,12 @@
   </si>
   <si>
     <t xml:space="preserve">S13, S11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">无（乘用车不在应税清单内）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S39, S40</t>
   </si>
   <si>
     <r>
@@ -3602,736 +3836,13 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">S37, S38, S39</t>
+    <t xml:space="preserve">S37, S38, S49</t>
   </si>
   <si>
     <t xml:space="preserve">结论：对增程式而言，车龄不改变税率，只通过“完税价格”和“报废税档位”影响总税费；这一点与燃油车和并联混动（车龄直接决定适用的统一税率）明显不同。</t>
   </si>
   <si>
     <t xml:space="preserve">中国增程式汽车进口：白俄罗斯与俄罗斯对比（新车与二手车）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关税由联盟统一，差别来自各国国内的税费；俄罗斯数据来自俄罗斯官方来源和报关数据库</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白俄罗斯</t>
-  </si>
-  <si>
-    <t xml:space="preserve">俄罗斯</t>
-  </si>
-  <si>
-    <t xml:space="preserve">差异</t>
-  </si>
-  <si>
-    <t xml:space="preserve">税则编码与关税</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8703 80 000 5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15%</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">相同（联盟统一税则）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S26, S01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">个人进口计税方式</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">关税 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ 20% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">增值税（综合海关支付）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">关税 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">消费税 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ 22% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">增值税（综合海关支付，电动机驱动车辆不适用按排量计的统一税率）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">联盟规则相同，但俄罗斯多一项消费税</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S13, S32, S30</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-01-01 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起，第 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">425-ФЗ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">号联邦法）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">俄罗斯高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个百分点</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">S13, S33, S34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对乘用车不征</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">按马力征收（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）：≤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">90 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">90–150 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">64 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">卢布</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">150–200 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">613 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">卢布</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力；更高档位更高（本次未取得）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">增程车普遍在 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">150 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力以上，俄罗斯消费税可达数十万卢布</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">S21, S35, S36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">报废税（个人）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">固定：≤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">624.92 BYN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt;3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,282.02 BYN</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">增程式和纯电车只有 ≤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">80 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力才适用个人优惠，否则按商业税率（按 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分钟最大功率、车龄计）；例：理想 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">L7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">197 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年约 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">219.4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">万卢布</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">最大的差别所在</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S18, S37, S39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">报废税（法人）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按类型和车龄分档（金额待查）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">两国都随车龄上升</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S06, S38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">电动车优惠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">纯电动车有配额和增值税减免；增程式没有</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年无电动车关税配额；增程式没有</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">对增程式两国都没有优惠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S03, S28</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">新车 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">二手车</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">关税和增值税税率不变；个人报废税满 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年翻倍</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">关税税率不变；报废税按车龄系数上升</t>
-  </si>
-  <si>
-    <t xml:space="preserve">两国关税都不随车龄变化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S27, S18, S37</t>
   </si>
   <si>
     <r>
@@ -4342,7 +3853,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">结论：同一辆中国增程车，白俄的税费主要是 </t>
+      <t xml:space="preserve">关税由联盟统一，差别来自各国国内税费。“核实结果”列说明每项差异如何被确认：两国官方来源 </t>
     </r>
     <r>
       <rPr>
@@ -4353,7 +3864,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">15% </t>
+      <t xml:space="preserve">/ </t>
     </r>
     <r>
       <rPr>
@@ -4363,7 +3874,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">关税和 </t>
+      <t xml:space="preserve">多个独立来源一致 </t>
     </r>
     <r>
       <rPr>
@@ -4374,7 +3885,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20% </t>
+      <t xml:space="preserve">/ </t>
     </r>
     <r>
       <rPr>
@@ -4384,28 +3895,1993 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">增值税（约为完税价格的 </t>
-    </r>
+      <t xml:space="preserve">仅单一来源或未取得</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">白俄罗斯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">俄罗斯</t>
+  </si>
+  <si>
+    <t xml:space="preserve">差异与影响</t>
+  </si>
+  <si>
+    <t xml:space="preserve">核实结果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">税则编码与关税</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8703 80 000 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15%</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">无差异（联盟统一税则）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已核实：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EEC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">委员会第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">81 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号决定，白俄海关与俄方数据库一致</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S26, S01, S27</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-01-01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025-11-28 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">425-ФЗ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号联邦法）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">俄罗斯高 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个百分点；两国税基均为完税价格 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">关税（俄罗斯还要加消费税）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已核实：白俄海关说明；俄罗斯税务局与 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">КонсультантПлюс </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一致</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S13, S33, S34</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不征：《税法典》第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">150 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">条应税消费品清单（酒、烟、燃料、机油、电子烟、能量饮料等）中没有乘用车</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">按功率征收（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，卢布</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力）：≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90–150</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">64</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">150–200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">613</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200–300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1004</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300–400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1711</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">400–500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：未独立核实；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt;500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1829</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1902</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1978</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">差异最明确的一项。增程车功率普遍 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt;150 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力，例：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">197 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× 613 = 120,761 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">卢布</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">白俄：财政部与税务部一致；俄罗斯：两家财税媒体一致，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">90–200 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力档另有 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">КонсультантПлюс </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">佐证</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S39, S40, S43, S44, S35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">个人进口计税方式</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">关税 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ 20% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">增值税，一次缴清</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">关税 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消费税 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ 22% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">增值税，一次缴清；电动机驱动车辆不适用按排量计的统一税率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">规则同源（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EEC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">理事会第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">107 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号决定），俄罗斯多出消费税</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">白俄：海关与 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BelTA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">38% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">算法一致；俄罗斯：仅 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TKS.RU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">说明</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S13, S22, S32, S30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">报废税：个人</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">固定额：出厂 ≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">624.92 BYN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt;3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,282.02 BYN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；不论动力类型、排量、功率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基础额 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万卢布 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">系数（按功率、车龄）。个人优惠 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,400 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">卢布（≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 5,200 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">卢布（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt;3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年）：燃油车限 ≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">160 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力；增程式和纯电车限 ≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力（按电机 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分钟最大功率，以车辆证书为准）。超出则按商业系数：例理想 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">197 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力）约 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">219.4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万卢布；新车 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt;205.95 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千瓦系数 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">152</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（约 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">304 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万卢布）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">最大的差距来源：同一辆增程车，白俄约 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">625 BYN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，俄罗斯可达 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万–</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万卢布</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">白俄：部长会议第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">195 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">号决议，经 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pravo.by </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">与 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BelTA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">确认；俄罗斯：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">КонсультантПлюс</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ГАРАНТ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TKS.RU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一致（理想 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">金额仅见 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">TKS.RU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">S18, S24, S37, S46, S47, S49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">报废税：经其他成员国转入</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EAEU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">成员国输入的车辆在白俄登记时一般要缴白俄报废税（在成员国登记满 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年等情形除外）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-04-01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起，个人自白俄、哈萨克斯坦、吉尔吉斯斯坦、亚美尼亚输入的车辆，或用于转售的车辆，按商业规则缴纳</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">两国都封堵了“先在别国清关再转入”的做法</t>
+  </si>
+  <si>
+    <t xml:space="preserve">各有一条来源</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S20, S45, S48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">报废税：法人</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">按车辆类型、车龄分档；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025-02-10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平均上调约一倍，官方说明是为与俄罗斯 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年起的税率“对齐”；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-04-29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">再上调约 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">M1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">类混动和电动车不适用优惠档</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">商业系数（按功率、车龄），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025-12-01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起加入功率维度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">白俄法人水平向俄罗斯 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年水平靠拢，但俄罗斯 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025-12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以后按功率再次加码</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">白俄法人具体金额仍未取得</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S41, S42, S18, S19, S37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">电动车优惠</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">纯电动车有关税配额（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">万辆，已用完）和增值税减免；增程式没有</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年无电动车关税配额；增程式没有</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">对增程式，两国都没有优惠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已核实</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S03, S16, S28</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新车 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">二手车</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">关税、增值税税率不随车龄变化；个人报废税满 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年约翻倍</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">关税税率不随车龄变化；报废税按车龄采用不同系数（超过 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年更高），个人优惠额 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3,400 → 5,200 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">卢布</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">两国关税都不随车龄变化，车龄通过报废税起作用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S27, S18, S37</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">38%</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结论：同一辆中国增程车，白俄的税费主要是 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），再加少量报废税；俄罗斯在此基础上多了按马力征收的消费税、更高的增值税，以及与功率挂钩的高额报废税，总税费通常是白俄的数倍。量化示例见“俄罗斯对比测算”。</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15% </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">关税和 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20% </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">增值税（约为完税价格的 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">38%</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），再加几百白俄卢布的报废税；俄罗斯多了按马力征收的消费税、更高的增值税，以及按功率计征、通常达数百万卢布的报废税，总税费约为白俄的 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍以上。量化示例见“俄罗斯对比测算”。</t>
     </r>
   </si>
   <si>
@@ -5589,7 +7065,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">俄罗斯报废税规则复杂（按功率、排量、车龄的系数），本表只把报废税作为输入项，默认值取 </t>
+      <t xml:space="preserve">俄罗斯报废税 </t>
     </r>
     <r>
       <rPr>
@@ -5600,7 +7076,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">TKS.RU </t>
+      <t xml:space="preserve">= </t>
     </r>
     <r>
       <rPr>
@@ -5610,7 +7086,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">报道的理想 </t>
+      <t xml:space="preserve">基础额 </t>
     </r>
     <r>
       <rPr>
@@ -5621,7 +7097,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">L7</t>
+      <t xml:space="preserve">× </t>
     </r>
     <r>
       <rPr>
@@ -5631,7 +7107,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（</t>
+      <t xml:space="preserve">系数（系数按功率、车龄查条例表格）；增程式个人进口只有 ≤</t>
     </r>
     <r>
       <rPr>
@@ -5642,7 +7118,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">197 </t>
+      <t xml:space="preserve">80 </t>
     </r>
     <r>
       <rPr>
@@ -5652,7 +7128,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">马力）</t>
+      <t xml:space="preserve">马力才适用优惠额。默认系数取 </t>
     </r>
     <r>
       <rPr>
@@ -5663,7 +7139,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026 </t>
+      <t xml:space="preserve">TKS.RU </t>
     </r>
     <r>
       <rPr>
@@ -5673,7 +7149,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年数据；马力超过 </t>
+      <t xml:space="preserve">报道的理想 </t>
     </r>
     <r>
       <rPr>
@@ -5684,7 +7160,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">200 </t>
+      <t xml:space="preserve">L7</t>
     </r>
     <r>
       <rPr>
@@ -5694,187 +7170,61 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">时消费税单价需手工填写</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">完税价格（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">USD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">取自“白俄税费测算”的新车场景</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">汇率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">RUB/USD</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">【示例值，非实时汇率】</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">发动机</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">电机功率（马力，按俄方计征口径）</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">（</t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">消费税按车辆功率；报废税按 </t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">197 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30 </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力）</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分钟最大功率（以 </t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ПТС </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年金额反推（</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">记载为准）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">消费税单价（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&gt;200 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力时手工填写，卢布</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力）</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">219.4 </t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -5883,7 +7233,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">本次未取得 </t>
+      <t xml:space="preserve">万 </t>
     </r>
     <r>
       <rPr>
@@ -5894,7 +7244,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026 </t>
+      <t xml:space="preserve">÷ 2 </t>
     </r>
     <r>
       <rPr>
@@ -5904,7 +7254,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年 </t>
+      <t xml:space="preserve">万 </t>
     </r>
     <r>
       <rPr>
@@ -5915,7 +7265,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">200 </t>
+      <t xml:space="preserve">= 109.7</t>
     </r>
     <r>
       <rPr>
@@ -5925,34 +7275,86 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">马力以上各档单价，请查《俄罗斯税法典》第 </t>
-    </r>
+      <t xml:space="preserve">），请按车型替换</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">完税价格（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">USD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">取自“白俄税费测算”的新车场景</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">汇率 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RUB/USD</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【示例值，非实时汇率】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">功率（马力）</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">193 </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消费税按车辆功率；报废税按电机 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">条</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">报废税（卢布）</t>
-  </si>
-  <si>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30 </t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -5961,40 +7363,90 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">默认：理想 </t>
-    </r>
+      <t xml:space="preserve">分钟最大功率（以车辆证书为准），两者可能不同</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消费税 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">400–500 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力档单价（卢布</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力）</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">L7</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本档 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">197 </t>
-    </r>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年单价未独立核实，功率在该档时请手工填写</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">车龄（年）</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -6003,7 +7455,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">马力）</t>
+      <t xml:space="preserve">影响个人优惠额（≤</t>
     </r>
     <r>
       <rPr>
@@ -6014,7 +7466,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026 </t>
+      <t xml:space="preserve">3 </t>
     </r>
     <r>
       <rPr>
@@ -6024,7 +7476,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年约 </t>
+      <t xml:space="preserve">年 </t>
     </r>
     <r>
       <rPr>
@@ -6035,7 +7487,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">219.4 </t>
+      <t xml:space="preserve">3,400</t>
     </r>
     <r>
       <rPr>
@@ -6045,7 +7497,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">万卢布（</t>
+      <t xml:space="preserve">；</t>
     </r>
     <r>
       <rPr>
@@ -6056,7 +7508,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">TKS.RU</t>
+      <t xml:space="preserve">&gt;3 </t>
     </r>
     <r>
       <rPr>
@@ -6066,13 +7518,8 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）；请按车型和车龄替换</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">俄罗斯增值税税率</t>
-  </si>
-  <si>
+      <t xml:space="preserve">年 </t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -6082,7 +7529,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026-01-01 </t>
+      <t xml:space="preserve">5,200</t>
     </r>
     <r>
       <rPr>
@@ -6092,116 +7539,11 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">起</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">关税税率</t>
-  </si>
-  <si>
-    <t xml:space="preserve">与白俄相同</t>
-  </si>
-  <si>
-    <t xml:space="preserve">俄罗斯（卢布）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">消费税单价（卢布</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">俄罗斯应缴合计</t>
-  </si>
-  <si>
-    <t xml:space="preserve">俄罗斯合计占完税价格</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白俄罗斯（同一辆车，个人，新车）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">白俄应缴合计（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">BYN</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">白俄合计占完税价格</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">俄罗斯合计占比 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷ </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">白俄合计占比（倍）</t>
-    </r>
+      <t xml:space="preserve">）和商业系数</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">报废税基础额（卢布）</t>
   </si>
   <si>
     <r>
@@ -6212,7 +7554,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">依据：俄罗斯增值税 </t>
+      <t xml:space="preserve">第 </t>
     </r>
     <r>
       <rPr>
@@ -6223,7 +7565,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">22%</t>
+      <t xml:space="preserve">1291 </t>
     </r>
     <r>
       <rPr>
@@ -6233,71 +7575,81 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
+      <t xml:space="preserve">号政府决定</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">报废税系数（商业）</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">S33, S34</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">按功率、车龄查表；默认值为理想 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；消费税 </t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L7 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">金额反推；新车 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年档位（</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt;205.95 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">S35, S36</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">千瓦为 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；报废税规则和理想 </t>
-    </r>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">152</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">俄罗斯增值税税率</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -6307,7 +7659,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">L7 </t>
+      <t xml:space="preserve">2026-01-01 </t>
     </r>
     <r>
       <rPr>
@@ -6317,97 +7669,208 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">示例（</t>
-    </r>
+      <t xml:space="preserve">起</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">关税税率</t>
+  </si>
+  <si>
+    <t xml:space="preserve">与白俄相同</t>
+  </si>
+  <si>
+    <t xml:space="preserve">俄罗斯（卢布，个人自用进口）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消费税单价（卢布</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">俄罗斯应缴合计</t>
+  </si>
+  <si>
+    <t xml:space="preserve">俄罗斯合计占完税价格</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白俄罗斯（同一辆车，个人，新车）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">白俄应缴合计（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BYN</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">白俄合计占完税价格</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">俄罗斯合计占比 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">白俄合计占比（倍）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">分项差异（占完税价格）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关税</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">S37, S39</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">依据：增值税 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）；个人进口电动机驱动车辆按 </t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22%</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15% + </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">消费税 </t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S33, S34</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+ </t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；消费税 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">增值税计（</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">S32</t>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年档位（</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
         <color rgb="FF595959"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。用占完税价格的比例对比，可以避免两国汇率差异的影响；但报废税和消费税是按卢布定额的，汇率输入值会影响俄罗斯的比例。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">论证思路与数据来源</t>
-  </si>
-  <si>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S43, S44, S35</t>
+    </r>
     <r>
       <rPr>
         <i val="true"/>
@@ -6416,7 +7879,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">先确定归类，再推出计税方式，最后分析个人</t>
+      <t xml:space="preserve">）；报废税规则、</t>
     </r>
     <r>
       <rPr>
@@ -6427,7 +7890,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
+      <t xml:space="preserve">80 </t>
     </r>
     <r>
       <rPr>
@@ -6437,6 +7900,126 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">马力门槛和系数（</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S37, S46, S47, S49</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）；个人进口电动机驱动车辆按 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15% + </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消费税 </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">增值税计（</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">S32</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。报废税和消费税是按卢布定额的，汇率输入值会影响俄罗斯的占比。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">论证思路与数据来源</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">先确定归类，再推出计税方式，最后分析个人</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">法人、车龄和国别差异；每一步都给出证据和来源</t>
     </r>
   </si>
@@ -7135,16 +8718,33 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">S33, S35, S37, S39</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">报废税示例来自 </t>
+    <t xml:space="preserve">S33, S39, S43, S37, S46, S49</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各差异项已逐项核实（见“白俄与俄罗斯对比”的“核实结果”列）；理想 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">L7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的具体金额只见于 </t>
     </r>
     <r>
       <rPr>
@@ -7161,7 +8761,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">（第三方），因此标为“中”；测算器中可以替换</t>
+      <t xml:space="preserve">，测算器中可替换</t>
     </r>
   </si>
   <si>
@@ -7245,15 +8845,15 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">200 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">马力以上的消费税单价、俄罗斯报废税完整系数表、燃油车个人统一税率的具体数值。</t>
+      <t xml:space="preserve">400–500 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">马力档消费税单价、俄罗斯报废税完整系数表、燃油车个人统一税率的具体数值。</t>
     </r>
   </si>
   <si>
@@ -8004,6 +9604,9 @@
     <t xml:space="preserve">https://pravo.by/novosti/obshchestvenno-politicheskie-i-v-oblasti-prava/2024/november/79682/</t>
   </si>
   <si>
+    <t xml:space="preserve">S21</t>
+  </si>
+  <si>
     <t xml:space="preserve">BelTA</t>
   </si>
   <si>
@@ -8373,6 +9976,225 @@
   </si>
   <si>
     <t xml:space="preserve">S39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白俄财政部</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Акцизы (Глава 15 Налогового кодекса)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（消费税章节，应税消费品清单）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.minfin.gov.by/ru/tax_policy/tax_system/doc/92aa7b734d3b48a6.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S40</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Комментарий: изменения 2026 года в части акцизов</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年消费税变化）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://nalog.gov.by/clarifications/comments/33596/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S41</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Изменение ставок утилизационного сбора с 10 февраля 2025 года</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（上调并与俄罗斯对齐）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.customs.gov.by/news/izmenenie-stavok-utilizatsionnogo-sbora-s-10-fevralya-2025-goda/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Минпром: изменения по уплате утильсбора на авто для импортеров-физлиц минимальны</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://belta.by/economics/view/minprom-izmenenija-po-uplate-utilsbora-na-avto-dlja-importerov-fizlits-minimalny-695013-2025/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РНК (rnk.ru)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Новые ставки акцизов в 2026 году: таблица</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第三方财税媒体（俄）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rnk.ru/article/146592-stavki-aktsizov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Учет. Налоги. Право (gazeta-unp.ru)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рост ставок на акцизы в 2026 году: новые тарифы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.gazeta-unp.ru/articles/53417-stavki-na-aktsizy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Утилизационный сбор с 1 апреля 2026 года: изменения для физлиц и юрлиц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.gazeta-unp.ru/articles/53281-utilizatsionnyy-sbor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ГАРАНТ.РУ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Утильсбор с 1 декабря 2025 года: новые правила расчета утилизационного сбора на автомобили</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.garant.ru/article/1901763/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S47</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Постановление Правительства РФ от 26.12.2013 N 1291 (ред. от 06.02.2026)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（报废税条例）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.consultant.ru/document/cons_doc_LAW_156832/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">С 1 апреля 2026 года изменятся правила расчета утильсбора для авто из Беларуси</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.alta.ru/ts_news/126709/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S49</t>
   </si>
   <si>
     <r>
@@ -8667,7 +10489,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8825,6 +10647,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="172" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -9264,8 +11090,8 @@
       <c r="D12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>27</v>
+      <c r="E12" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9507,8 +11333,8 @@
       <c r="E10" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>27</v>
+      <c r="F10" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9714,16 +11540,16 @@
         <v>66</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>27</v>
+        <v>99</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9731,13 +11557,13 @@
         <v>70</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>11</v>
@@ -9745,16 +11571,16 @@
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>27</v>
@@ -9762,16 +11588,16 @@
     </row>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>11</v>
@@ -9779,16 +11605,16 @@
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>11</v>
@@ -9796,16 +11622,16 @@
     </row>
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>62</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>27</v>
@@ -9813,16 +11639,16 @@
     </row>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>11</v>
@@ -9837,7 +11663,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -9876,7 +11702,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9887,7 +11713,7 @@
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -9907,7 +11733,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -9921,16 +11747,16 @@
         <v>37</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>6</v>
@@ -9941,22 +11767,22 @@
     </row>
     <row r="6" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G6" s="11" t="s">
         <v>11</v>
@@ -9964,7 +11790,7 @@
     </row>
     <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>58</v>
@@ -9976,10 +11802,10 @@
         <v>58</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>11</v>
@@ -9987,22 +11813,22 @@
     </row>
     <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>27</v>
@@ -10010,22 +11836,22 @@
     </row>
     <row r="9" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>11</v>
@@ -10033,22 +11859,22 @@
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>27</v>
@@ -10056,22 +11882,22 @@
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>11</v>
@@ -10088,7 +11914,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -10102,16 +11928,16 @@
         <v>37</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>6</v>
@@ -10122,22 +11948,22 @@
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G15" s="12" t="s">
         <v>27</v>
@@ -10154,7 +11980,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -10168,16 +11994,16 @@
         <v>37</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>6</v>
@@ -10191,19 +12017,19 @@
         <v>51</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>11</v>
@@ -10214,19 +12040,19 @@
         <v>70</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>27</v>
@@ -10243,7 +12069,7 @@
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -10272,36 +12098,39 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2"/>
@@ -10310,209 +12139,262 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E4" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G4" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="F5" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="G5" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>176</v>
+        <v>94</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>177</v>
+        <v>58</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="F6" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="F7" s="11" t="s">
+    <row r="9" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="G9" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F8" s="12" t="s">
+    <row r="10" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="F9" s="12" t="s">
+    <row r="11" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="F11" s="11" t="s">
+    <row r="12" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+    <row r="13" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A15:G15"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10540,7 +12422,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -10551,7 +12433,7 @@
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -10572,7 +12454,7 @@
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2"/>
       <c r="B4" s="15" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -10583,7 +12465,7 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2"/>
       <c r="B5" s="16" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C5" s="17" t="n">
         <v>3</v>
@@ -10592,13 +12474,13 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="18" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="16" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="C6" s="19" t="n">
         <v>0.15</v>
@@ -10607,13 +12489,13 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="20" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="16" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="C7" s="19" t="n">
         <v>0.2</v>
@@ -10622,13 +12504,13 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="20" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
       <c r="B8" s="16" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="C8" s="21" t="n">
         <v>624.92</v>
@@ -10637,13 +12519,13 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="18" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="16" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="C9" s="21" t="n">
         <v>1282.02</v>
@@ -10652,13 +12534,13 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="18" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="16" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="C10" s="22" t="n">
         <v>0</v>
@@ -10667,7 +12549,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="18" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10682,7 +12564,7 @@
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="15" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -10696,25 +12578,25 @@
         <v>37</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="16" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>0.5</v>
@@ -10729,13 +12611,13 @@
         <v>6</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="16" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C15" s="24" t="n">
         <v>35000</v>
@@ -10750,13 +12632,13 @@
         <v>19000</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="16" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="C16" s="22" t="n">
         <v>0</v>
@@ -10771,7 +12653,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10786,7 +12668,7 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="15" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -10800,25 +12682,25 @@
         <v>37</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
       <c r="B20" s="16" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C20" s="25" t="n">
         <f aca="false">C15*$C$5</f>
@@ -10841,7 +12723,7 @@
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
       <c r="B21" s="16" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="C21" s="25" t="n">
         <f aca="false">C20*$C$6</f>
@@ -10860,13 +12742,13 @@
         <v>8550</v>
       </c>
       <c r="G21" s="27" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
       <c r="B22" s="16" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="C22" s="25" t="n">
         <f aca="false">(C20+C21)*$C$7</f>
@@ -10885,13 +12767,13 @@
         <v>13110</v>
       </c>
       <c r="G22" s="27" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
       <c r="B23" s="16" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="C23" s="25" t="n">
         <f aca="false">C21+C22</f>
@@ -10914,7 +12796,7 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="28" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="C24" s="29" t="n">
         <f aca="false">IF(C20=0,0,C23/C20)</f>
@@ -10933,13 +12815,13 @@
         <v>0.38</v>
       </c>
       <c r="G24" s="27" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="16" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="C25" s="25" t="n">
         <f aca="false">IF(C14&lt;=3,$C$8,$C$9)</f>
@@ -10958,13 +12840,13 @@
         <v>1282.02</v>
       </c>
       <c r="G25" s="27" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="28" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C26" s="30" t="n">
         <f aca="false">C23+C25+$C$10</f>
@@ -10987,7 +12869,7 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
       <c r="B27" s="28" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C27" s="29" t="n">
         <f aca="false">IF(C20=0,0,C26/C20)</f>
@@ -11010,7 +12892,7 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
       <c r="B28" s="16" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="C28" s="25" t="n">
         <f aca="false">C23+C16+$C$10</f>
@@ -11029,13 +12911,13 @@
         <v>21660</v>
       </c>
       <c r="G28" s="27" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2"/>
       <c r="B29" s="16" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="C29" s="25" t="n">
         <f aca="false">C22</f>
@@ -11054,13 +12936,13 @@
         <v>13110</v>
       </c>
       <c r="G29" s="27" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="16" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="C30" s="25" t="n">
         <f aca="false">C28-C29</f>
@@ -11083,7 +12965,7 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
       <c r="B31" s="28" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="C31" s="29" t="n">
         <f aca="false">IF(C20=0,0,C30/C20)</f>
@@ -11106,7 +12988,7 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2"/>
       <c r="B32" s="16" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="C32" s="25" t="n">
         <f aca="false">IF($C$5=0,0,C26/$C$5)</f>
@@ -11137,7 +13019,7 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -11166,19 +13048,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11188,7 +13070,7 @@
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11215,7 +13097,7 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2"/>
       <c r="B5" s="16" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="C5" s="31" t="n">
         <f aca="false">白俄税费测算!C15</f>
@@ -11223,134 +13105,136 @@
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="18" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2"/>
       <c r="B6" s="16" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="C6" s="32" t="n">
         <v>80</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="18" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="F6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2"/>
       <c r="B7" s="16" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="C7" s="33" t="n">
         <v>197</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="18" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
       <c r="B8" s="16" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="C8" s="34" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="18" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="C9" s="34" t="n">
-        <v>2194000</v>
+        <v>281</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>0.5</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="18" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>0.22</v>
+        <v>283</v>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>20000</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="20" t="s">
-        <v>267</v>
+      <c r="E10" s="18" t="s">
+        <v>284</v>
       </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>0.15</v>
+        <v>285</v>
+      </c>
+      <c r="C11" s="32" t="n">
+        <v>109.7</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="18" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="F11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>0.22</v>
+      </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="E12" s="20" t="s">
+        <v>288</v>
+      </c>
       <c r="F12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
-      <c r="B13" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="C13" s="2"/>
+      <c r="B13" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>0.15</v>
+      </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="E13" s="18" t="s">
+        <v>290</v>
+      </c>
       <c r="F13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
-      <c r="B14" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="C14" s="35" t="n">
-        <f aca="false">C5*C6</f>
-        <v>2800000</v>
-      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
-      <c r="B15" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="35" t="n">
-        <f aca="false">C14*C11</f>
-        <v>420000</v>
-      </c>
+      <c r="B15" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -11358,11 +13242,11 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2"/>
       <c r="B16" s="16" t="s">
-        <v>271</v>
+        <v>136</v>
       </c>
       <c r="C16" s="35" t="n">
-        <f aca="false">IF(C7&lt;=90,0,IF(C7&lt;=150,64,IF(C7&lt;=200,613,C8)))</f>
-        <v>613</v>
+        <f aca="false">C5*C6</f>
+        <v>2800000</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -11371,11 +13255,11 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
       <c r="B17" s="16" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C17" s="35" t="n">
-        <f aca="false">C7*C16</f>
-        <v>120761</v>
+        <f aca="false">C16*C13</f>
+        <v>420000</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -11384,11 +13268,11 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2"/>
       <c r="B18" s="16" t="s">
-        <v>94</v>
+        <v>292</v>
       </c>
       <c r="C18" s="35" t="n">
-        <f aca="false">(C14+C15+C17)*C10</f>
-        <v>734967.42</v>
+        <f aca="false">IF(C7&lt;=90,0,IF(C7&lt;=150,64,IF(C7&lt;=200,613,IF(C7&lt;=300,1004,IF(C7&lt;=400,1711,IF(C7&lt;=500,C8,1829))))))</f>
+        <v>613</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -11397,11 +13281,11 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="16" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C19" s="35" t="n">
-        <f aca="false">C9</f>
-        <v>2194000</v>
+        <f aca="false">C7*C18</f>
+        <v>120761</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -11409,12 +13293,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2"/>
-      <c r="B20" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="C20" s="36" t="n">
-        <f aca="false">C15+C17+C18+C19</f>
-        <v>3469728.42</v>
+      <c r="B20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="35" t="n">
+        <f aca="false">(C16+C17+C19)*C12</f>
+        <v>734967.42</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -11422,12 +13306,12 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2"/>
-      <c r="B21" s="28" t="s">
-        <v>273</v>
-      </c>
-      <c r="C21" s="29" t="n">
-        <f aca="false">IF(C14=0,0,C20/C14)</f>
-        <v>1.23918872142857</v>
+      <c r="B21" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="35" t="n">
+        <f aca="false">IF(C7&lt;=80,IF(C9&lt;=3,3400,5200),C10*C11)</f>
+        <v>2194000</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -11435,44 +13319,44 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="B22" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="C22" s="36" t="n">
+        <f aca="false">C17+C19+C20+C21</f>
+        <v>3469728.42</v>
+      </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2"/>
-      <c r="B23" s="15" t="s">
-        <v>274</v>
-      </c>
-      <c r="C23" s="2"/>
+      <c r="B23" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="C23" s="29" t="n">
+        <f aca="false">IF(C16=0,0,C22/C16)</f>
+        <v>1.23918872142857</v>
+      </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
-      <c r="B24" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="C24" s="37" t="n">
-        <f aca="false">白俄税费测算!C26</f>
-        <v>40524.92</v>
-      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
-      <c r="B25" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="C25" s="38" t="n">
-        <f aca="false">白俄税费测算!C27</f>
-        <v>0.385951619047619</v>
-      </c>
+      <c r="B25" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -11480,11 +13364,11 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2"/>
       <c r="B26" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="C26" s="39" t="n">
-        <f aca="false">IF(C25=0,0,C21/C25)</f>
-        <v>3.21073590644966</v>
+        <v>296</v>
+      </c>
+      <c r="C26" s="37" t="n">
+        <f aca="false">白俄税费测算!C26</f>
+        <v>40524.92</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -11492,26 +13376,148 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
+      <c r="B27" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="C27" s="38" t="n">
+        <f aca="false">白俄税费测算!C27</f>
+        <v>0.385951619047619</v>
+      </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
     </row>
-    <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2"/>
+      <c r="B28" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="C28" s="39" t="n">
+        <f aca="false">IF(C27=0,0,C23/C27)</f>
+        <v>3.21073590644966</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2"/>
+      <c r="B31" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2"/>
+      <c r="B32" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="C32" s="40" t="n">
+        <f aca="false">C17/C16</f>
+        <v>0.15</v>
+      </c>
+      <c r="D32" s="40" t="n">
+        <f aca="false">白俄税费测算!C21/白俄税费测算!C20</f>
+        <v>0.15</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2"/>
+      <c r="B33" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="40" t="n">
+        <f aca="false">C19/C16</f>
+        <v>0.0431289285714286</v>
+      </c>
+      <c r="D33" s="40" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2"/>
+      <c r="B34" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="40" t="n">
+        <f aca="false">C20/C16</f>
+        <v>0.262488364285714</v>
+      </c>
+      <c r="D34" s="40" t="n">
+        <f aca="false">白俄税费测算!C22/白俄税费测算!C20</f>
+        <v>0.23</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2"/>
+      <c r="B35" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="40" t="n">
+        <f aca="false">C21/C16</f>
+        <v>0.783571428571429</v>
+      </c>
+      <c r="D35" s="40" t="n">
+        <f aca="false">白俄税费测算!C25/白俄税费测算!C20</f>
+        <v>0.00595161904761905</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A37:F37"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11528,7 +13534,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -11541,7 +13547,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -11551,7 +13557,7 @@
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -11569,7 +13575,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -11579,19 +13585,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>7</v>
@@ -11602,16 +13608,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>45</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>11</v>
@@ -11622,16 +13628,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>11</v>
@@ -11642,16 +13648,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>11</v>
@@ -11662,16 +13668,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>74</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>27</v>
@@ -11682,16 +13688,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>11</v>
@@ -11702,19 +13708,19 @@
         <v>6</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>27</v>
+        <v>330</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11727,7 +13733,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -11737,7 +13743,7 @@
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -11747,7 +13753,7 @@
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -11757,7 +13763,7 @@
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -11775,7 +13781,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -11785,19 +13791,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="F19" s="2"/>
     </row>
@@ -11806,736 +13812,916 @@
         <v>87</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E20" s="40" t="s">
-        <v>321</v>
+        <v>343</v>
+      </c>
+      <c r="E20" s="41" t="s">
+        <v>344</v>
       </c>
       <c r="F20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>324</v>
+        <v>343</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>347</v>
       </c>
       <c r="F21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E22" s="40" t="s">
-        <v>327</v>
+        <v>343</v>
+      </c>
+      <c r="E22" s="41" t="s">
+        <v>350</v>
       </c>
       <c r="F22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E23" s="40" t="s">
-        <v>330</v>
+        <v>343</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>353</v>
       </c>
       <c r="F23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E24" s="40" t="s">
-        <v>333</v>
+        <v>343</v>
+      </c>
+      <c r="E24" s="41" t="s">
+        <v>356</v>
       </c>
       <c r="F24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E25" s="40" t="s">
-        <v>336</v>
+        <v>343</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>359</v>
       </c>
       <c r="F25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>339</v>
+        <v>343</v>
+      </c>
+      <c r="E26" s="41" t="s">
+        <v>362</v>
       </c>
       <c r="F26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E27" s="40" t="s">
-        <v>342</v>
+        <v>343</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>365</v>
       </c>
       <c r="F27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C28" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E28" s="40" t="s">
-        <v>344</v>
+      <c r="E28" s="41" t="s">
+        <v>367</v>
       </c>
       <c r="F28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E29" s="40" t="s">
-        <v>347</v>
+        <v>343</v>
+      </c>
+      <c r="E29" s="41" t="s">
+        <v>370</v>
       </c>
       <c r="F29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E30" s="40" t="s">
-        <v>351</v>
+        <v>343</v>
+      </c>
+      <c r="E30" s="41" t="s">
+        <v>374</v>
       </c>
       <c r="F30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="E31" s="40" t="s">
-        <v>354</v>
+        <v>343</v>
+      </c>
+      <c r="E31" s="41" t="s">
+        <v>377</v>
       </c>
       <c r="F31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="E32" s="40" t="s">
-        <v>358</v>
+        <v>380</v>
+      </c>
+      <c r="E32" s="41" t="s">
+        <v>381</v>
       </c>
       <c r="F32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="E33" s="40" t="s">
-        <v>361</v>
+        <v>380</v>
+      </c>
+      <c r="E33" s="41" t="s">
+        <v>384</v>
       </c>
       <c r="F33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="E34" s="40" t="s">
-        <v>364</v>
+        <v>380</v>
+      </c>
+      <c r="E34" s="41" t="s">
+        <v>387</v>
       </c>
       <c r="F34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="E35" s="40" t="s">
-        <v>367</v>
+        <v>380</v>
+      </c>
+      <c r="E35" s="41" t="s">
+        <v>390</v>
       </c>
       <c r="F35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="E36" s="40" t="s">
-        <v>370</v>
+        <v>380</v>
+      </c>
+      <c r="E36" s="41" t="s">
+        <v>393</v>
       </c>
       <c r="F36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="E37" s="40" t="s">
-        <v>373</v>
+        <v>380</v>
+      </c>
+      <c r="E37" s="41" t="s">
+        <v>396</v>
       </c>
       <c r="F37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="E38" s="40" t="s">
-        <v>376</v>
+        <v>380</v>
+      </c>
+      <c r="E38" s="41" t="s">
+        <v>399</v>
       </c>
       <c r="F38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="E39" s="40" t="s">
-        <v>379</v>
+        <v>380</v>
+      </c>
+      <c r="E39" s="41" t="s">
+        <v>402</v>
       </c>
       <c r="F39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>69</v>
+        <v>403</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="E40" s="40" t="s">
-        <v>383</v>
+        <v>406</v>
+      </c>
+      <c r="E40" s="41" t="s">
+        <v>407</v>
       </c>
       <c r="F40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="E41" s="40" t="s">
-        <v>385</v>
+        <v>406</v>
+      </c>
+      <c r="E41" s="41" t="s">
+        <v>409</v>
       </c>
       <c r="F41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="E42" s="40" t="s">
-        <v>388</v>
+        <v>406</v>
+      </c>
+      <c r="E42" s="41" t="s">
+        <v>412</v>
       </c>
       <c r="F42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="E43" s="40" t="s">
-        <v>391</v>
+        <v>406</v>
+      </c>
+      <c r="E43" s="41" t="s">
+        <v>415</v>
       </c>
       <c r="F43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="E44" s="40" t="s">
-        <v>394</v>
+        <v>406</v>
+      </c>
+      <c r="E44" s="41" t="s">
+        <v>418</v>
       </c>
       <c r="F44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="E45" s="40" t="s">
-        <v>398</v>
+        <v>421</v>
+      </c>
+      <c r="E45" s="41" t="s">
+        <v>422</v>
       </c>
       <c r="F45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="E46" s="40" t="s">
-        <v>401</v>
+        <v>421</v>
+      </c>
+      <c r="E46" s="41" t="s">
+        <v>425</v>
       </c>
       <c r="F46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="E47" s="40" t="s">
-        <v>404</v>
+        <v>421</v>
+      </c>
+      <c r="E47" s="41" t="s">
+        <v>428</v>
       </c>
       <c r="F47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="E48" s="40" t="s">
-        <v>407</v>
+        <v>421</v>
+      </c>
+      <c r="E48" s="41" t="s">
+        <v>431</v>
       </c>
       <c r="F48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E49" s="40" t="s">
-        <v>412</v>
+        <v>435</v>
+      </c>
+      <c r="E49" s="41" t="s">
+        <v>436</v>
       </c>
       <c r="F49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E50" s="40" t="s">
-        <v>416</v>
+        <v>435</v>
+      </c>
+      <c r="E50" s="41" t="s">
+        <v>440</v>
       </c>
       <c r="F50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="E51" s="40" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="E51" s="41" t="s">
+        <v>444</v>
       </c>
       <c r="F51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>422</v>
+        <v>446</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E52" s="40" t="s">
-        <v>423</v>
+        <v>435</v>
+      </c>
+      <c r="E52" s="41" t="s">
+        <v>447</v>
       </c>
       <c r="F52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>424</v>
+        <v>448</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E53" s="40" t="s">
-        <v>427</v>
+        <v>435</v>
+      </c>
+      <c r="E53" s="41" t="s">
+        <v>451</v>
       </c>
       <c r="F53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E54" s="40" t="s">
-        <v>430</v>
+        <v>435</v>
+      </c>
+      <c r="E54" s="41" t="s">
+        <v>454</v>
       </c>
       <c r="F54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E55" s="40" t="s">
-        <v>433</v>
+        <v>435</v>
+      </c>
+      <c r="E55" s="41" t="s">
+        <v>457</v>
       </c>
       <c r="F55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="C56" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="D56" s="9" t="s">
         <v>435</v>
       </c>
-      <c r="D56" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E56" s="40" t="s">
-        <v>436</v>
+      <c r="E56" s="41" t="s">
+        <v>460</v>
       </c>
       <c r="F56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E57" s="40" t="s">
-        <v>439</v>
+        <v>435</v>
+      </c>
+      <c r="E57" s="41" t="s">
+        <v>463</v>
       </c>
       <c r="F57" s="2"/>
     </row>
-    <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>440</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>418</v>
+        <v>464</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>465</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="E58" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="E58" s="41" t="s">
+        <v>467</v>
+      </c>
+      <c r="F58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E59" s="41" t="s">
+        <v>470</v>
+      </c>
+      <c r="F59" s="2"/>
+    </row>
+    <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E60" s="41" t="s">
+        <v>473</v>
+      </c>
+      <c r="F60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="E61" s="41" t="s">
+        <v>476</v>
+      </c>
+      <c r="F61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="E62" s="41" t="s">
+        <v>481</v>
+      </c>
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="E63" s="41" t="s">
+        <v>485</v>
+      </c>
+      <c r="F63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>483</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="E64" s="41" t="s">
+        <v>488</v>
+      </c>
+      <c r="F64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="E65" s="41" t="s">
+        <v>492</v>
+      </c>
+      <c r="F65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="E66" s="41" t="s">
+        <v>495</v>
+      </c>
+      <c r="F66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E67" s="41" t="s">
+        <v>498</v>
+      </c>
+      <c r="F67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="B68" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="F58" s="2"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2"/>
-      <c r="B60" s="28" t="s">
-        <v>443</v>
-      </c>
-      <c r="C60" s="28" t="n">
-        <f aca="false">COUNTIF(D20:D58,"白俄*")</f>
-        <v>25</v>
-      </c>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2"/>
-      <c r="B61" s="28" t="s">
-        <v>444</v>
-      </c>
-      <c r="C61" s="41" t="n">
-        <f aca="false">C60/COUNTA(A20:A58)</f>
-        <v>0.641025641025641</v>
-      </c>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
+      <c r="C68" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E68" s="41" t="s">
+        <v>501</v>
+      </c>
+      <c r="F68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2"/>
+      <c r="B70" s="28" t="s">
+        <v>502</v>
+      </c>
+      <c r="C70" s="28" t="n">
+        <f aca="false">COUNTIF(D20:D68,"白俄*")</f>
+        <v>29</v>
+      </c>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="C71" s="42" t="n">
+        <f aca="false">C70/COUNTA(A20:A68)</f>
+        <v>0.591836734693878</v>
+      </c>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -12583,7 +14769,17 @@
     <hyperlink ref="E55" r:id="rId36" display="https://www.nalog.gov.ru/rn27/news/tax_doc_news/16590707/"/>
     <hyperlink ref="E56" r:id="rId37" display="https://www.consultant.ru/legalnews/29989/"/>
     <hyperlink ref="E57" r:id="rId38" display="https://www.consultant.ru/law/hotdocs/91326.html"/>
-    <hyperlink ref="E58" r:id="rId39" display="https://www.tks.ru/autonews/2025/09/18/0004/kakie-modeli-avto-mogut-propast-v-rossii-iz-za-novyih-pravil-utilsbora/"/>
+    <hyperlink ref="E58" r:id="rId39" display="https://www.minfin.gov.by/ru/tax_policy/tax_system/doc/92aa7b734d3b48a6.html"/>
+    <hyperlink ref="E59" r:id="rId40" display="https://nalog.gov.by/clarifications/comments/33596/"/>
+    <hyperlink ref="E60" r:id="rId41" display="https://www.customs.gov.by/news/izmenenie-stavok-utilizatsionnogo-sbora-s-10-fevralya-2025-goda/"/>
+    <hyperlink ref="E61" r:id="rId42" display="https://belta.by/economics/view/minprom-izmenenija-po-uplate-utilsbora-na-avto-dlja-importerov-fizlits-minimalny-695013-2025/"/>
+    <hyperlink ref="E62" r:id="rId43" display="https://www.rnk.ru/article/146592-stavki-aktsizov"/>
+    <hyperlink ref="E63" r:id="rId44" display="https://www.gazeta-unp.ru/articles/53417-stavki-na-aktsizy"/>
+    <hyperlink ref="E64" r:id="rId45" display="https://www.gazeta-unp.ru/articles/53281-utilizatsionnyy-sbor"/>
+    <hyperlink ref="E65" r:id="rId46" display="https://www.garant.ru/article/1901763/"/>
+    <hyperlink ref="E66" r:id="rId47" display="https://www.consultant.ru/document/cons_doc_LAW_156832/"/>
+    <hyperlink ref="E67" r:id="rId48" display="https://www.alta.ru/ts_news/126709/"/>
+    <hyperlink ref="E68" r:id="rId49" display="https://www.tks.ru/autonews/2025/09/18/0004/kakie-modeli-avto-mogut-propast-v-rossii-iz-za-novyih-pravil-utilsbora/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
